--- a/content/post/drafts/season-prediction/men_simple-model-tests-predicted_rmse.xlsx
+++ b/content/post/drafts/season-prediction/men_simple-model-tests-predicted_rmse.xlsx
@@ -636,25 +636,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>0.187428351213043</v>
+        <v>0.185570637258237</v>
       </c>
       <c r="C10" t="n">
-        <v>0.143217287836576</v>
+        <v>0.144830853155986</v>
       </c>
       <c r="D10" t="n">
-        <v>0.14886636190323</v>
+        <v>0.152318913687851</v>
       </c>
       <c r="E10" t="n">
-        <v>0.167027814023225</v>
+        <v>0.176889748641919</v>
       </c>
       <c r="F10" t="n">
-        <v>0.147141989932391</v>
+        <v>0.153029849049339</v>
       </c>
       <c r="G10" t="n">
-        <v>0.180678181192513</v>
+        <v>0.180312413515609</v>
       </c>
       <c r="H10" t="n">
-        <v>0.16239333101683</v>
+        <v>0.165492069218157</v>
       </c>
     </row>
     <row r="11">
